--- a/resources/比赛/测试-辨识学生数据.xlsx
+++ b/resources/比赛/测试-辨识学生数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="14140"/>
+    <workbookView windowWidth="28260" windowHeight="14120"/>
   </bookViews>
   <sheets>
     <sheet name="理学院-辨识学生数据" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="44">
   <si>
-    <t>学生姓名</t>
+    <t>姓名</t>
   </si>
   <si>
     <t>学号</t>
@@ -137,7 +137,7 @@
     <t>非校外住宿</t>
   </si>
   <si>
-    <t xml:space="preserve">卫美娟  </t>
+    <t xml:space="preserve">卫美娟        </t>
   </si>
   <si>
     <t>1220910003</t>
@@ -882,16 +882,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>754380</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:rowOff>34290</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>910419</xdr:colOff>
+      <xdr:colOff>807549</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>21590</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -912,7 +912,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11658600" y="1222375"/>
+          <a:off x="11555730" y="1243965"/>
           <a:ext cx="897255" cy="1196975"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -924,16 +924,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>800735</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1203960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>830709</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>774194</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1191260</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -954,7 +954,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11658600" y="2432050"/>
+          <a:off x="11602085" y="2413635"/>
           <a:ext cx="817880" cy="1196975"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -966,16 +966,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>774065</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1184910</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>850900</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>767715</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1172210</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -996,7 +996,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11658600" y="3641725"/>
+          <a:off x="11575415" y="3604260"/>
           <a:ext cx="838200" cy="1196975"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1008,16 +1008,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>819150</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:rowOff>52705</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>833594</xdr:colOff>
+      <xdr:colOff>795494</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>40005</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1038,7 +1038,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11658600" y="4851400"/>
+          <a:off x="11620500" y="4891405"/>
           <a:ext cx="820420" cy="1196975"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
